--- a/besprechung/Mapping-Sitzung_14a.xlsx
+++ b/besprechung/Mapping-Sitzung_14a.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,6 +121,12 @@
       <color rgb="004A5A63"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="005A6A73"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -186,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -251,6 +257,7 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -853,7 +860,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gelb ausfüllen. „Anzeige?“ = vermutlich reiner Formulartext — erst Entscheidung 1 klären.</t>
+          <t>Die Spalte "Quelle in epilot" ist bewusst leer: Für § 14a liegt noch kein Mapping-Vorschlag vor (Billing hat nur die Einspeiser-Strecke zugeordnet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Vorschläge erzeugen statt raten: umsetzung/tools/schema_attribute.py liest die Attribute des epilot-Schemas aus und ordnet sie den Spalten nach Namensähnlichkeit zu.</t>
         </is>
       </c>
     </row>
